--- a/Outputs/Scenarios/PtX_demand_BG_Ammonia.xlsx
+++ b/Outputs/Scenarios/PtX_demand_BG_Ammonia.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.0009103253911235636</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001516180492622159</v>
+        <v>0.001913808322212921</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.0003140126653194275</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.003032360985244317</v>
+        <v>0.00251210132255542</v>
       </c>
     </row>
     <row r="20">
@@ -1481,7 +1481,7 @@
         <v>1.311624796363922e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0005053934975407196</v>
+        <v>0.0003140126653194275</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.001347625912720067</v>
       </c>
       <c r="K30" t="n">
-        <v>0.008093295968494873</v>
+        <v>0.01021581352220822</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.001676183970610802</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.01618659193698975</v>
+        <v>0.01340947176488642</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>7.092767961684565e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.002697765322831625</v>
+        <v>0.001676183970610802</v>
       </c>
     </row>
     <row r="43">
